--- a/scripts/checks/results/HLR_results_03_>75_lg_families_tPBC.xlsx
+++ b/scripts/checks/results/HLR_results_03_>75_lg_families_tPBC.xlsx
@@ -553,66 +553,66 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>962</v>
+        <v>1182</v>
       </c>
       <c r="E2" t="n">
-        <v>960</v>
+        <v>1180</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3077269933674377</v>
+        <v>0.2430222915463953</v>
       </c>
       <c r="H2" t="n">
-        <v>426.7361442702318</v>
+        <v>378.8305795828101</v>
       </c>
       <c r="I2" t="n">
-        <v>9.971253084328792e-79</v>
+        <v>2.142744421722969e-73</v>
       </c>
       <c r="J2" t="n">
-        <v>110.0735669101074</v>
+        <v>138.3668153787242</v>
       </c>
       <c r="K2" t="n">
-        <v>159.0031185031185</v>
+        <v>182.7884940778342</v>
       </c>
       <c r="L2" t="n">
-        <v>48.92955159301106</v>
+        <v>44.42167869910998</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1146599655313619</v>
+        <v>0.1172600130328171</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1654558985464292</v>
+        <v>0.1547743387619256</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{'const': 0.7486643282984455, 'N1ratio-ArgsPreds': -0.2076128570460793}</t>
+          <t>{'const': 0.5838997183381505, 'N1ratio-ArgsPreds': -2.2076993978570845}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{'const': 3.609420076864592e-116, 'N1ratio-ArgsPreds': 9.971253084334582e-79}</t>
+          <t>{'const': 7.775219821683825e-118, 'N1ratio-ArgsPreds': 2.142744421721985e-73}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5547314605892099}</t>
+          <t>{'N1ratio-ArgsPreds': -0.49297291157465767}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5547314605892107)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.49297291157465845)}</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5547314605892106)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.49297291157465845)}</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(30.772699336743898)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(24.3022291546396)}</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -628,80 +628,80 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>['N1ratio-ArgsPreds', 'latitude', 'longitude', 'Macro_class']</t>
+          <t>['N1ratio-ArgsPreds', 'Macro_class']</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>962</v>
+        <v>1182</v>
       </c>
       <c r="E3" t="n">
-        <v>957</v>
+        <v>1179</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.479592843275045</v>
+        <v>0.3567957206318101</v>
       </c>
       <c r="H3" t="n">
-        <v>220.4861833101157</v>
+        <v>327.005096295468</v>
       </c>
       <c r="I3" t="n">
-        <v>4.294307191675612e-134</v>
+        <v>1.051214650344987e-113</v>
       </c>
       <c r="J3" t="n">
-        <v>82.74636081060896</v>
+        <v>117.57034161013</v>
       </c>
       <c r="K3" t="n">
-        <v>159.0031185031185</v>
+        <v>182.7884940778342</v>
       </c>
       <c r="L3" t="n">
-        <v>19.06418942312738</v>
+        <v>32.6090762338521</v>
       </c>
       <c r="M3" t="n">
-        <v>0.08646432686584009</v>
+        <v>0.0997203915268278</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1654558985464292</v>
+        <v>0.1547743387619256</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{'const': 0.5012613697993361, 'N1ratio-ArgsPreds': -0.18759216212886268, 'latitude': 0.003859565124336087, 'longitude': -0.0011643109332120708, 'Macro_class': 0.10590781317939046}</t>
+          <t>{'const': 0.42043285066495284, 'N1ratio-ArgsPreds': -2.2218401403568935, 'Macro_class': 0.07788445136296299}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{'const': 3.1320277999482196e-59, 'N1ratio-ArgsPreds': 1.1215140527897133e-71, 'latitude': 1.8428053396941623e-09, 'longitude': 6.6296048584200996e-12, 'Macro_class': 1.7758055341238104e-48}</t>
+          <t>{'const': 6.930717994676659e-63, 'N1ratio-ArgsPreds': 4.939686204018216e-85, 'Macro_class': 1.1960987595172436e-43}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5012371371091685, 'latitude': 0.15579690691392784, 'longitude': -0.21881401539051057, 'Macro_class': 0.4363972243934317}</t>
+          <t>{'N1ratio-ArgsPreds': -0.49613049861242414, 'Macro_class': 0.3373179500728017}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5335917062944944), 'latitude': np.float64(0.19254033199315904), 'longitude': np.float64(-0.21927839710687763), 'Macro_class': np.float64(0.44780549421579474)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.5260728260218384), 'Macro_class': np.float64(0.3876848934536315)}</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4551375768731756), 'latitude': np.float64(0.14154560503599223), 'longitude': np.float64(-0.1621317014180825), 'Macro_class': np.float64(0.36129329107632996)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4961087612322976), 'Macro_class': np.float64(0.3373031708795736)}</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(20.715021388198583), 'latitude': np.float64(2.0035158305005107), 'longitude': np.float64(2.6286688604722253), 'Macro_class': np.float64(13.05328421767657)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(24.612390297144486), 'Macro_class': np.float64(11.377342908541484)}</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>0.1718658499076073</v>
+        <v>0.1137734290854148</v>
       </c>
       <c r="V3" t="n">
-        <v>105.3505998371635</v>
+        <v>208.5478551595873</v>
       </c>
       <c r="W3" t="n">
-        <v>6.152793725703289e-59</v>
+        <v>1.196098759517543e-43</v>
       </c>
     </row>
     <row r="4">
@@ -713,80 +713,80 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>['N1ratio-ArgsPreds', 'latitude', 'longitude', 'Macro_class', 'Fam_class']</t>
+          <t>['N1ratio-ArgsPreds', 'Macro_class', 'Fam_class']</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>962</v>
+        <v>1182</v>
       </c>
       <c r="E4" t="n">
-        <v>956</v>
+        <v>1178</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4796152051467759</v>
+        <v>0.3569959740880773</v>
       </c>
       <c r="H4" t="n">
-        <v>176.2204202179437</v>
+        <v>218.008618157216</v>
       </c>
       <c r="I4" t="n">
-        <v>6.655474998894777e-133</v>
+        <v>1.789150003396864e-112</v>
       </c>
       <c r="J4" t="n">
-        <v>82.74280520326819</v>
+        <v>117.533737582425</v>
       </c>
       <c r="K4" t="n">
-        <v>159.0031185031185</v>
+        <v>182.7884940778342</v>
       </c>
       <c r="L4" t="n">
-        <v>15.25206265997006</v>
+        <v>21.75158549846972</v>
       </c>
       <c r="M4" t="n">
-        <v>0.08655105146785376</v>
+        <v>0.09977397078304331</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1654558985464292</v>
+        <v>0.1547743387619256</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{'const': 0.5022521165134609, 'N1ratio-ArgsPreds': -0.1868596228725078, 'latitude': 0.003861911675352187, 'longitude': -0.0011726761380343716, 'Macro_class': 0.10605541705456357, 'Fam_class': -6.335276171803566e-05}</t>
+          <t>{'const': 0.41595982391071945, 'N1ratio-ArgsPreds': -2.2414576983872205, 'Macro_class': 0.07804745806789978, 'Fam_class': 0.0001536810867590469}</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{'const': 5.8731439146671465e-58, 'N1ratio-ArgsPreds': 1.021100727284747e-63, 'latitude': 1.8474541409507328e-09, 'longitude': 1.890703154937315e-11, 'Macro_class': 4.467737364813494e-48, 'Fam_class': 0.8394246983393954}</t>
+          <t>{'const': 6.599951616340036e-57, 'N1ratio-ArgsPreds': 7.071562641472498e-80, 'Macro_class': 1.0857045464289004e-43, 'Fam_class': 0.5448322963964947}</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.49927982782977987, 'latitude': 0.15589162882648708, 'longitude': -0.22038612469956084, 'Macro_class': 0.4370054318476462, 'Fam_class': -0.005141289176141133}</t>
+          <t>{'N1ratio-ArgsPreds': -0.5005110427705565, 'Macro_class': 0.33802393293067867, 'Fam_class': 0.014828456985821685}</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.507053421123803), 'latitude': np.float64(0.19262632455533082), 'longitude': np.float64(-0.2146730787235208), 'Macro_class': np.float64(0.4462948780477885), 'Fam_class': np.float64(-0.006555147159176553)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.5121172767786071), 'Macro_class': np.float64(0.38801559902695193), 'Fam_class': np.float64(0.017644751553077983)}</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.42437692775634), 'latitude': np.float64(0.1416082152282626), 'longitude': np.float64(-0.15855682404396443), 'Macro_class': np.float64(0.359763009298949), 'Fam_class': np.float64(-0.004728834077302492)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.478107785842693), 'Macro_class': np.float64(0.3375893068246497), 'Fam_class': np.float64(0.014151093818749218)}</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(18.009577681190983), 'latitude': np.float64(2.0052886620133945), 'longitude': np.float64(2.51402664509087), 'Macro_class': np.float64(12.942942285983566), 'Fam_class': np.float64(0.0022361871730657307)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(22.858705488340235), 'Macro_class': np.float64(11.396654008234748), 'Fam_class': np.float64(0.02002534562670423)}</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>2.236187173088044e-05</v>
+        <v>0.0002002534562671743</v>
       </c>
       <c r="V4" t="n">
-        <v>0.04108104154109925</v>
+        <v>0.3668695093287708</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8394246983391191</v>
+        <v>0.5448322963965472</v>
       </c>
     </row>
     <row r="5">
@@ -798,80 +798,80 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>['N1ratio-ArgsPreds', 'latitude', 'longitude', 'Macro_class', 'Fam_class', 'Nlen_freq', 'Vlen_freq']</t>
+          <t>['N1ratio-ArgsPreds', 'Macro_class', 'Fam_class', 'Nlen_freq', 'Vlen_freq']</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>962</v>
+        <v>1182</v>
       </c>
       <c r="E5" t="n">
-        <v>954</v>
+        <v>1176</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4899845368979755</v>
+        <v>0.3608503965538552</v>
       </c>
       <c r="H5" t="n">
-        <v>130.9330744482489</v>
+        <v>132.7889633535823</v>
       </c>
       <c r="I5" t="n">
-        <v>8.390176564638851e-135</v>
+        <v>1.158898468228028e-111</v>
       </c>
       <c r="J5" t="n">
-        <v>81.09404911803406</v>
+        <v>116.8291935043657</v>
       </c>
       <c r="K5" t="n">
-        <v>159.0031185031185</v>
+        <v>182.7884940778342</v>
       </c>
       <c r="L5" t="n">
-        <v>11.12986705501206</v>
+        <v>13.1918601146937</v>
       </c>
       <c r="M5" t="n">
-        <v>0.08500424435852627</v>
+        <v>0.09934455229963068</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1654558985464292</v>
+        <v>0.1547743387619256</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>{'const': 0.3483767834119514, 'N1ratio-ArgsPreds': -0.1711022620550383, 'latitude': 0.004130703479984807, 'longitude': -0.0013150306758518595, 'Macro_class': 0.10009547794010427, 'Fam_class': -0.0006149714696248368, 'Nlen_freq': -0.01820089026954685, 'Vlen_freq': 0.04449842893550047}</t>
+          <t>{'const': 0.4080769520720633, 'N1ratio-ArgsPreds': -2.156788804960809, 'Macro_class': 0.07213034190350322, 'Fam_class': -0.00010875434157404129, 'Nlen_freq': -0.2653828352075616, 'Vlen_freq': 0.4014977147297475}</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>{'const': 1.3508935437593632e-06, 'N1ratio-ArgsPreds': 2.0118916735882568e-50, 'latitude': 1.5473436766201869e-10, 'longitude': 2.9594703377156323e-13, 'Macro_class': 9.06208432530112e-40, 'Fam_class': 0.06712240191054994, 'Nlen_freq': 0.26824614531785695, 'Vlen_freq': 0.00044341186477892984}</t>
+          <t>{'const': 2.2596589821348784e-21, 'N1ratio-ArgsPreds': 4.5028870178793945e-70, 'Macro_class': 3.874576589350147e-33, 'Fam_class': 0.6893973889384314, 'Nlen_freq': 0.08773693996979007, 'Vlen_freq': 0.009462887528995972}</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.457176925795317, 'latitude': 0.1667417972823901, 'longitude': -0.24713943186208256, 'Macro_class': 0.4124472731148397, 'Fam_class': -0.0499069981272446, 'Nlen_freq': -0.04303296638783078, 'Vlen_freq': 0.1492535958795391}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4816047229370061, 'Macro_class': 0.3123968731005309, 'Fam_class': -0.010493542894972379, 'Nlen_freq': -0.06622671289629932, 'Vlen_freq': 0.10950154803404274}</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4566524854190465), 'latitude': np.float64(0.20507553709004792), 'longitude': np.float64(-0.2330257573585506), 'Macro_class': np.float64(0.4086019713193097), 'Fam_class': np.float64(-0.05923953233639515), 'Nlen_freq': np.float64(-0.03584190101211122), 'Vlen_freq': np.float64(0.11339379054596245)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.48359277861672084), 'Macro_class': np.float64(0.3393596909691059), 'Fam_class': np.float64(-0.011656782888603237), 'Nlen_freq': np.float64(-0.04977021031584832), 'Vlen_freq': np.float64(0.07557554484450098)}</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.3665731724096174), 'latitude': np.float64(0.14963578392179924), 'longitude': np.float64(-0.17112723603352595), 'Macro_class': np.float64(0.3197113447403103), 'Fam_class': np.float64(-0.04238055824704733), 'Nlen_freq': np.float64(-0.025613082221695012), 'Vlen_freq': np.float64(0.08150629710847035)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.44170016365104275), 'Macro_class': np.float64(0.28842331961400464), 'Fam_class': np.float64(-0.00931986191210442), 'Nlen_freq': np.float64(-0.03983907946458818), 'Vlen_freq': np.float64(0.06059354704574537)}</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(13.437589073045109), 'latitude': np.float64(2.239086782989139), 'longitude': np.float64(2.9284530912474103), 'Macro_class': np.float64(10.221534395565754), 'Fam_class': np.float64(0.17961117173313718), 'Nlen_freq': np.float64(0.0656029980895309), 'Vlen_freq': np.float64(0.6643276468334242)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(19.509903456935795), 'Macro_class': np.float64(8.318801129716228), 'Fam_class': np.float64(0.008685982606069466), 'Nlen_freq': np.float64(0.15871522525857718), 'Vlen_freq': np.float64(0.36715779435849577)}</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>0.01036933175119958</v>
+        <v>0.00385442246577794</v>
       </c>
       <c r="V5" t="n">
-        <v>9.698080946876624</v>
+        <v>3.545962318770956</v>
       </c>
       <c r="W5" t="n">
-        <v>6.767394114055434e-05</v>
+        <v>0.02914962989156372</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/checks/results/HLR_results_03_>75_lg_families_tPBC.xlsx
+++ b/scripts/checks/results/HLR_results_03_>75_lg_families_tPBC.xlsx
@@ -562,57 +562,57 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2430222915463953</v>
+        <v>0.2355842238404511</v>
       </c>
       <c r="H2" t="n">
-        <v>378.8305795828101</v>
+        <v>363.662541775839</v>
       </c>
       <c r="I2" t="n">
-        <v>2.142744421722969e-73</v>
+        <v>6.968483886006474e-71</v>
       </c>
       <c r="J2" t="n">
-        <v>138.3668153787242</v>
+        <v>138.7796194903806</v>
       </c>
       <c r="K2" t="n">
-        <v>182.7884940778342</v>
+        <v>181.5499153976311</v>
       </c>
       <c r="L2" t="n">
-        <v>44.42167869910998</v>
+        <v>42.7702959072505</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1172600130328171</v>
+        <v>0.1176098470257463</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1547743387619256</v>
+        <v>0.1537255845873253</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{'const': 0.5838997183381505, 'N1ratio-ArgsPreds': -2.2076993978570845}</t>
+          <t>{'const': 0.5682328519626636, 'N1ratio-ArgsPreds': -2.118622554728008}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{'const': 7.775219821683825e-118, 'N1ratio-ArgsPreds': 2.142744421721985e-73}</t>
+          <t>{'const': 4.267556190895944e-115, 'N1ratio-ArgsPreds': 6.968483886004664e-71}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.49297291157465767}</t>
+          <t>{'N1ratio-ArgsPreds': -0.48537019257516306}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.49297291157465845)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.48537019257516234)}</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.49297291157465845)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4853701925751624)}</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(24.3022291546396)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(23.558422384045024)}</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -641,67 +641,67 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3567957206318101</v>
+        <v>0.3492337762636348</v>
       </c>
       <c r="H3" t="n">
-        <v>327.005096295468</v>
+        <v>316.3552495478238</v>
       </c>
       <c r="I3" t="n">
-        <v>1.051214650344987e-113</v>
+        <v>1.032856147522481e-110</v>
       </c>
       <c r="J3" t="n">
-        <v>117.57034161013</v>
+        <v>118.146552862973</v>
       </c>
       <c r="K3" t="n">
-        <v>182.7884940778342</v>
+        <v>181.5499153976311</v>
       </c>
       <c r="L3" t="n">
-        <v>32.6090762338521</v>
+        <v>31.70168126732907</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0997203915268278</v>
+        <v>0.1002091203248287</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1547743387619256</v>
+        <v>0.1537255845873253</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{'const': 0.42043285066495284, 'N1ratio-ArgsPreds': -2.2218401403568935, 'Macro_class': 0.07788445136296299}</t>
+          <t>{'const': 0.4045200691938263, 'N1ratio-ArgsPreds': -2.12763953992686, 'Macro_class': 0.07757591894969838}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{'const': 6.930717994676659e-63, 'N1ratio-ArgsPreds': 4.939686204018216e-85, 'Macro_class': 1.1960987595172436e-43}</t>
+          <t>{'const': 1.575410238077618e-59, 'N1ratio-ArgsPreds': 9.437566588744387e-82, 'Macro_class': 3.7077239398332485e-43}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.49613049861242414, 'Macro_class': 0.3373179500728017}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4874359573489059, 'Macro_class': 0.33712582192304164}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5260728260218384), 'Macro_class': np.float64(0.3876848934536315)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.5171506606682962), 'Macro_class': np.float64(0.38558403529664403)}</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4961087612322976), 'Macro_class': np.float64(0.3373031708795736)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.48742680633232016), 'Macro_class': np.float64(0.33711949279622594)}</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(24.612390297144486), 'Macro_class': np.float64(11.377342908541484)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(23.758489153132516), 'Macro_class': np.float64(11.364955242318462)}</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>0.1137734290854148</v>
+        <v>0.1136495524231838</v>
       </c>
       <c r="V3" t="n">
-        <v>208.5478551595873</v>
+        <v>205.9000873426032</v>
       </c>
       <c r="W3" t="n">
-        <v>1.196098759517543e-43</v>
+        <v>3.707723939836159e-43</v>
       </c>
     </row>
     <row r="4">
@@ -726,67 +726,67 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3569959740880773</v>
+        <v>0.3492609714554959</v>
       </c>
       <c r="H4" t="n">
-        <v>218.008618157216</v>
+        <v>210.7498327938574</v>
       </c>
       <c r="I4" t="n">
-        <v>1.789150003396864e-112</v>
+        <v>2.026215300087851e-109</v>
       </c>
       <c r="J4" t="n">
-        <v>117.533737582425</v>
+        <v>118.1416155781914</v>
       </c>
       <c r="K4" t="n">
-        <v>182.7884940778342</v>
+        <v>181.5499153976311</v>
       </c>
       <c r="L4" t="n">
-        <v>21.75158549846972</v>
+        <v>21.13609993981325</v>
       </c>
       <c r="M4" t="n">
-        <v>0.09977397078304331</v>
+        <v>0.1002899962463424</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1547743387619256</v>
+        <v>0.1537255845873253</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{'const': 0.41595982391071945, 'N1ratio-ArgsPreds': -2.2414576983872205, 'Macro_class': 0.07804745806789978, 'Fam_class': 0.0001536810867590469}</t>
+          <t>{'const': 0.4028340233159087, 'N1ratio-ArgsPreds': -2.1345183214926595, 'Macro_class': 0.07763441457018597, 'Fam_class': 5.6325726055794887e-05}</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{'const': 6.599951616340036e-57, 'N1ratio-ArgsPreds': 7.071562641472498e-80, 'Macro_class': 1.0857045464289004e-43, 'Fam_class': 0.5448322963964947}</t>
+          <t>{'const': 3.839914156120041e-54, 'N1ratio-ArgsPreds': 2.675478655394602e-76, 'Macro_class': 4.322341342704349e-43, 'Fam_class': 0.8244469015926568}</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5005110427705565, 'Macro_class': 0.33802393293067867, 'Fam_class': 0.014828456985821685}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4890118659626529, 'Macro_class': 0.3373800294709865, 'Fam_class': 0.005453291830189267}</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5121172767786071), 'Macro_class': np.float64(0.38801559902695193), 'Fam_class': np.float64(0.017644751553077983)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.5018946891589668), 'Macro_class': np.float64(0.38544880990627617), 'Fam_class': np.float64(0.006464479485016144)}</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.478107785842693), 'Macro_class': np.float64(0.3375893068246497), 'Fam_class': np.float64(0.014151093818749218)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.468096830579025), 'Macro_class': np.float64(0.33697358819231116), 'Fam_class': np.float64(0.005214900944498913)}</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(22.858705488340235), 'Macro_class': np.float64(11.396654008234748), 'Fam_class': np.float64(0.02002534562670423)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(21.911464279812844), 'Macro_class': np.float64(11.35511991392013), 'Fam_class': np.float64(0.002719519186093565)}</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>0.0002002534562671743</v>
+        <v>2.719519186111796e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3668695093287708</v>
+        <v>0.0492300824249794</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5448322963965472</v>
+        <v>0.8244469015914047</v>
       </c>
     </row>
     <row r="5">
@@ -811,67 +811,67 @@
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3608503965538552</v>
+        <v>0.3545170942653388</v>
       </c>
       <c r="H5" t="n">
-        <v>132.7889633535823</v>
+        <v>129.1783559725805</v>
       </c>
       <c r="I5" t="n">
-        <v>1.158898468228028e-111</v>
+        <v>3.719729292359789e-109</v>
       </c>
       <c r="J5" t="n">
-        <v>116.8291935043657</v>
+        <v>117.1873669267448</v>
       </c>
       <c r="K5" t="n">
-        <v>182.7884940778342</v>
+        <v>181.5499153976311</v>
       </c>
       <c r="L5" t="n">
-        <v>13.1918601146937</v>
+        <v>12.87250969417726</v>
       </c>
       <c r="M5" t="n">
-        <v>0.09934455229963068</v>
+        <v>0.09964912153634765</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1547743387619256</v>
+        <v>0.1537255845873253</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>{'const': 0.4080769520720633, 'N1ratio-ArgsPreds': -2.156788804960809, 'Macro_class': 0.07213034190350322, 'Fam_class': -0.00010875434157404129, 'Nlen_freq': -0.2653828352075616, 'Vlen_freq': 0.4014977147297475}</t>
+          <t>{'const': 0.40661879615305585, 'N1ratio-ArgsPreds': -2.0417210982057794, 'Macro_class': 0.0708228152030555, 'Fam_class': -0.00023527710716803773, 'Nlen_freq': -0.3472227393580949, 'Vlen_freq': 0.47237701852186653}</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>{'const': 2.2596589821348784e-21, 'N1ratio-ArgsPreds': 4.5028870178793945e-70, 'Macro_class': 3.874576589350147e-33, 'Fam_class': 0.6893973889384314, 'Nlen_freq': 0.08773693996979007, 'Vlen_freq': 0.009462887528995972}</t>
+          <t>{'const': 3.4606946180473786e-21, 'N1ratio-ArgsPreds': 1.365843532947458e-66, 'Macro_class': 4.657879342776414e-32, 'Fam_class': 0.38608704188327936, 'Nlen_freq': 0.02481469616122416, 'Vlen_freq': 0.002122959197660978}</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4816047229370061, 'Macro_class': 0.3123968731005309, 'Fam_class': -0.010493542894972379, 'Nlen_freq': -0.06622671289629932, 'Vlen_freq': 0.10950154803404274}</t>
+          <t>{'N1ratio-ArgsPreds': -0.46775229519263634, 'Macro_class': 0.30777849762521703, 'Fam_class': -0.022778840437477573, 'Nlen_freq': -0.08706200994837256, 'Vlen_freq': 0.12957205861125223}</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.48359277861672084), 'Macro_class': np.float64(0.3393596909691059), 'Fam_class': np.float64(-0.011656782888603237), 'Nlen_freq': np.float64(-0.04977021031584832), 'Vlen_freq': np.float64(0.07557554484450098)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.472624800758417), 'Macro_class': np.float64(0.33382556693384297), 'Fam_class': np.float64(-0.02527585041960119), 'Nlen_freq': np.float64(-0.06538824844943403), 'Vlen_freq': np.float64(0.08943443504499574)}</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.44170016365104275), 'Macro_class': np.float64(0.28842331961400464), 'Fam_class': np.float64(-0.00931986191210442), 'Nlen_freq': np.float64(-0.03983907946458818), 'Vlen_freq': np.float64(0.06059354704574537)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.43087666400357455), 'Macro_class': np.float64(0.2845237136429678), 'Fam_class': np.float64(-0.020313601204661216), 'Nlen_freq': np.float64(-0.05264686402866155), 'Vlen_freq': np.float64(0.07214246545177096)}</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(19.509903456935795), 'Macro_class': np.float64(8.318801129716228), 'Fam_class': np.float64(0.008685982606069466), 'Nlen_freq': np.float64(0.15871522525857718), 'Vlen_freq': np.float64(0.36715779435849577)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(18.56546995828493), 'Macro_class': np.float64(8.095374362518553), 'Fam_class': np.float64(0.04126423939020136), 'Nlen_freq': np.float64(0.27716922920523773), 'Vlen_freq': np.float64(0.5204535321459967)}</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>0.00385442246577794</v>
+        <v>0.005256122809842889</v>
       </c>
       <c r="V5" t="n">
-        <v>3.545962318770956</v>
+        <v>4.788043470601331</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02914962989156372</v>
+        <v>0.008491799873005476</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/checks/results/HLR_results_03_>75_lg_families_tPBC.xlsx
+++ b/scripts/checks/results/HLR_results_03_>75_lg_families_tPBC.xlsx
@@ -562,57 +562,57 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2355842238404511</v>
+        <v>0.2353905796617167</v>
       </c>
       <c r="H2" t="n">
-        <v>363.662541775839</v>
+        <v>363.2715954217998</v>
       </c>
       <c r="I2" t="n">
-        <v>6.968483886006474e-71</v>
+        <v>8.095008422521239e-71</v>
       </c>
       <c r="J2" t="n">
-        <v>138.7796194903806</v>
+        <v>138.8147755746471</v>
       </c>
       <c r="K2" t="n">
         <v>181.5499153976311</v>
       </c>
       <c r="L2" t="n">
-        <v>42.7702959072505</v>
+        <v>42.73513982298402</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1176098470257463</v>
+        <v>0.1176396403174976</v>
       </c>
       <c r="N2" t="n">
         <v>0.1537255845873253</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{'const': 0.5682328519626636, 'N1ratio-ArgsPreds': -2.118622554728008}</t>
+          <t>{'const': 0.5677540716261412, 'N1ratio-ArgsPreds': -2.114660301017572}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{'const': 4.267556190895944e-115, 'N1ratio-ArgsPreds': 6.968483886004664e-71}</t>
+          <t>{'const': 4.817730324087699e-115, 'N1ratio-ArgsPreds': 8.095008422516971e-71}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.48537019257516306}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4851706706528301}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.48537019257516234)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.48517067065282893)}</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4853701925751624)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.48517067065282893)}</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(23.558422384045024)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(23.53905796617158)}</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -641,67 +641,67 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3492337762636348</v>
+        <v>0.3491947428507135</v>
       </c>
       <c r="H3" t="n">
-        <v>316.3552495478238</v>
+        <v>316.3009189756378</v>
       </c>
       <c r="I3" t="n">
-        <v>1.032856147522481e-110</v>
+        <v>1.070028715544569e-110</v>
       </c>
       <c r="J3" t="n">
-        <v>118.146552862973</v>
+        <v>118.1536393757865</v>
       </c>
       <c r="K3" t="n">
         <v>181.5499153976311</v>
       </c>
       <c r="L3" t="n">
-        <v>31.70168126732907</v>
+        <v>31.6981380109223</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1002091203248287</v>
+        <v>0.1002151309379021</v>
       </c>
       <c r="N3" t="n">
         <v>0.1537255845873253</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{'const': 0.4045200691938263, 'N1ratio-ArgsPreds': -2.12763953992686, 'Macro_class': 0.07757591894969838}</t>
+          <t>{'const': 0.40405247376452097, 'N1ratio-ArgsPreds': -2.124365622184127, 'Macro_class': 0.0776289024453228}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{'const': 1.575410238077618e-59, 'N1ratio-ArgsPreds': 9.437566588744387e-82, 'Macro_class': 3.7077239398332485e-43}</t>
+          <t>{'const': 1.7698729514271043e-59, 'N1ratio-ArgsPreds': 9.778023530340503e-82, 'Macro_class': 3.306577763577906e-43}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4874359573489059, 'Macro_class': 0.33712582192304164}</t>
+          <t>{'N1ratio-ArgsPreds': -0.48739738157042417, 'Macro_class': 0.33735607513502514}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5171506606682962), 'Macro_class': np.float64(0.38558403529664403)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.5171081769389502), 'Macro_class': np.float64(0.38579736106583357)}</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.48742680633232016), 'Macro_class': np.float64(0.33711949279622594)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4873867644062604), 'Macro_class': np.float64(0.33734872637820523)}</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(23.758489153132516), 'Macro_class': np.float64(11.364955242318462)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(23.754585811840357), 'Macro_class': np.float64(11.380416318899718)}</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>0.1136495524231838</v>
+        <v>0.1138041631889968</v>
       </c>
       <c r="V3" t="n">
-        <v>205.9000873426032</v>
+        <v>206.1678311996934</v>
       </c>
       <c r="W3" t="n">
-        <v>3.707723939836159e-43</v>
+        <v>3.306577763578641e-43</v>
       </c>
     </row>
     <row r="4">
@@ -726,67 +726,67 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3492609714554959</v>
+        <v>0.3492231561018949</v>
       </c>
       <c r="H4" t="n">
-        <v>210.7498327938574</v>
+        <v>210.7147694560792</v>
       </c>
       <c r="I4" t="n">
-        <v>2.026215300087851e-109</v>
+        <v>2.096653304651258e-109</v>
       </c>
       <c r="J4" t="n">
-        <v>118.1416155781914</v>
+        <v>118.1484809524384</v>
       </c>
       <c r="K4" t="n">
         <v>181.5499153976311</v>
       </c>
       <c r="L4" t="n">
-        <v>21.13609993981325</v>
+        <v>21.13381148173092</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1002899962463424</v>
+        <v>0.1002958242380631</v>
       </c>
       <c r="N4" t="n">
         <v>0.1537255845873253</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{'const': 0.4028340233159087, 'N1ratio-ArgsPreds': -2.1345183214926595, 'Macro_class': 0.07763441457018597, 'Fam_class': 5.6325726055794887e-05}</t>
+          <t>{'const': 0.4023285843356037, 'N1ratio-ArgsPreds': -2.131393139964414, 'Macro_class': 0.07768887585019306, 'Fam_class': 5.757785284744886e-05}</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{'const': 3.839914156120041e-54, 'N1ratio-ArgsPreds': 2.675478655394602e-76, 'Macro_class': 4.322341342704349e-43, 'Fam_class': 0.8244469015926568}</t>
+          <t>{'const': 4.4540603906049116e-54, 'N1ratio-ArgsPreds': 2.768873736109067e-76, 'Macro_class': 3.847094873680971e-43, 'Fam_class': 0.8206291634371919}</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4890118659626529, 'Macro_class': 0.3373800294709865, 'Fam_class': 0.005453291830189267}</t>
+          <t>{'N1ratio-ArgsPreds': -0.48900971879207905, 'Macro_class': 0.3376167047696353, 'Fam_class': 0.005574519078933897}</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5018946891589668), 'Macro_class': np.float64(0.38544880990627617), 'Fam_class': np.float64(0.006464479485016144)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.5018513781681596), 'Macro_class': np.float64(0.38566609802934726), 'Fam_class': np.float64(0.006607466030716836)}</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.468096830579025), 'Macro_class': np.float64(0.33697358819231116), 'Fam_class': np.float64(0.005214900944498913)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.46805643617465753), 'Macro_class': np.float64(0.33720652721315586), 'Fam_class': np.float64(0.005330408162729559)}</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(21.911464279812844), 'Macro_class': np.float64(11.35511991392013), 'Fam_class': np.float64(0.002719519186093565)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(21.907682744452124), 'Macro_class': np.float64(11.370824199515681), 'Fam_class': np.float64(0.0028413251181293913)}</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>2.719519186111796e-05</v>
+        <v>2.841325118141391e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0492300824249794</v>
+        <v>0.05143208490827349</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8244469015914047</v>
+        <v>0.8206291634358905</v>
       </c>
     </row>
     <row r="5">
@@ -811,67 +811,67 @@
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3545170942653388</v>
+        <v>0.3544719695755855</v>
       </c>
       <c r="H5" t="n">
-        <v>129.1783559725805</v>
+        <v>129.1528846382756</v>
       </c>
       <c r="I5" t="n">
-        <v>3.719729292359789e-109</v>
+        <v>3.875077188192842e-109</v>
       </c>
       <c r="J5" t="n">
-        <v>117.1873669267448</v>
+        <v>117.1955593103519</v>
       </c>
       <c r="K5" t="n">
         <v>181.5499153976311</v>
       </c>
       <c r="L5" t="n">
-        <v>12.87250969417726</v>
+        <v>12.87087121745584</v>
       </c>
       <c r="M5" t="n">
-        <v>0.09964912153634765</v>
+        <v>0.09965608784893872</v>
       </c>
       <c r="N5" t="n">
         <v>0.1537255845873253</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>{'const': 0.40661879615305585, 'N1ratio-ArgsPreds': -2.0417210982057794, 'Macro_class': 0.0708228152030555, 'Fam_class': -0.00023527710716803773, 'Nlen_freq': -0.3472227393580949, 'Vlen_freq': 0.47237701852186653}</t>
+          <t>{'const': 0.4067219853575191, 'N1ratio-ArgsPreds': -2.038609946124187, 'Macro_class': 0.07087917977348535, 'Fam_class': -0.00023350941357384272, 'Nlen_freq': -0.3534945830476971, 'Vlen_freq': 0.4724557651202294}</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>{'const': 3.4606946180473786e-21, 'N1ratio-ArgsPreds': 1.365843532947458e-66, 'Macro_class': 4.657879342776414e-32, 'Fam_class': 0.38608704188327936, 'Nlen_freq': 0.02481469616122416, 'Vlen_freq': 0.002122959197660978}</t>
+          <t>{'const': 3.1418012839772783e-21, 'N1ratio-ArgsPreds': 1.520238562698623e-66, 'Macro_class': 4.286664584684698e-32, 'Fam_class': 0.38978795899575414, 'Nlen_freq': 0.023962418102818565, 'Vlen_freq': 0.002124208221448192}</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.46775229519263634, 'Macro_class': 0.30777849762521703, 'Fam_class': -0.022778840437477573, 'Nlen_freq': -0.08706200994837256, 'Vlen_freq': 0.12957205861125223}</t>
+          <t>{'N1ratio-ArgsPreds': -0.46772228820140077, 'Macro_class': 0.3080234441548975, 'Fam_class': -0.022607697520900652, 'Nlen_freq': -0.08760704159967515, 'Vlen_freq': 0.12961130072052524}</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.472624800758417), 'Macro_class': np.float64(0.33382556693384297), 'Fam_class': np.float64(-0.02527585041960119), 'Nlen_freq': np.float64(-0.06538824844943403), 'Vlen_freq': np.float64(0.08943443504499574)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4724755582836438), 'Macro_class': np.float64(0.33401223285199133), 'Fam_class': np.float64(-0.025079553115110058), 'Nlen_freq': np.float64(-0.06577945018790529), 'Vlen_freq': np.float64(0.08942934560020149)}</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.43087666400357455), 'Macro_class': np.float64(0.2845237136429678), 'Fam_class': np.float64(-0.020313601204661216), 'Nlen_freq': np.float64(-0.05264686402866155), 'Vlen_freq': np.float64(0.07214246545177096)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4307165492931905), 'Macro_class': np.float64(0.2847127349342342), 'Fam_class': np.float64(-0.020156446555294753), 'Nlen_freq': np.float64(-0.052965053169601), 'Vlen_freq': np.float64(0.07214084843598352)}</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(18.56546995828493), 'Macro_class': np.float64(8.095374362518553), 'Fam_class': np.float64(0.04126423939020136), 'Nlen_freq': np.float64(0.27716922920523773), 'Vlen_freq': np.float64(0.5204535321459967)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(18.55167458350334), 'Macro_class': np.float64(8.10613414337315), 'Fam_class': np.float64(0.04062823377364537), 'Nlen_freq': np.float64(0.28052968572586606), 'Vlen_freq': np.float64(0.5204302013063546)}</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>0.005256122809842889</v>
+        <v>0.00524881347369055</v>
       </c>
       <c r="V5" t="n">
-        <v>4.788043470601331</v>
+        <v>4.7810508251685</v>
       </c>
       <c r="W5" t="n">
-        <v>0.008491799873005476</v>
+        <v>0.008550905490501026</v>
       </c>
     </row>
   </sheetData>
